--- a/data/before.xlsx
+++ b/data/before.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{3CCFAF2E-6663-4988-AACF-A9214D4ABAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39A1A9A5-283D-4A12-A5B8-86E6D0518AB9}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{3CCFAF2E-6663-4988-AACF-A9214D4ABAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE07A008-80FD-48FD-9784-4B82934E23FC}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="6360" windowHeight="14520" xr2:uid="{AC69CF91-0B0A-4C72-8E2D-805D25D8DA4C}"/>
+    <workbookView xWindow="3510" yWindow="2310" windowWidth="8175" windowHeight="13890" xr2:uid="{AC69CF91-0B0A-4C72-8E2D-805D25D8DA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>鉄の巨人が作られた</t>
   </si>
   <si>
-    <t>ルブニールで樹熱が流行</t>
-  </si>
-  <si>
     <t>ジェルマ66日だけの栄華</t>
   </si>
   <si>
@@ -591,6 +588,13 @@
     <t>ノーランドとカルガラの出会い</t>
     <rPh sb="11" eb="13">
       <t>デア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルブニールで樹熱が流行(約）</t>
+    <rPh sb="12" eb="13">
+      <t>ヤク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1012,7 +1016,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>184</v>
       </c>
       <c r="B7">
         <v>460</v>
@@ -1020,7 +1024,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B8">
         <v>419</v>
@@ -1028,7 +1032,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>300</v>
@@ -1036,7 +1040,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>210</v>
@@ -1044,7 +1048,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>202</v>
@@ -1052,7 +1056,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <v>200</v>
@@ -1060,7 +1064,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>200</v>
@@ -1068,7 +1072,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -1076,7 +1080,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>102</v>
@@ -1084,7 +1088,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -1092,7 +1096,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>82</v>
@@ -1100,7 +1104,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>67</v>
@@ -1108,7 +1112,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>66</v>
@@ -1116,7 +1120,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20">
         <v>63</v>
@@ -1124,7 +1128,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21">
         <v>62</v>
@@ -1132,7 +1136,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22">
         <v>57</v>
@@ -1140,7 +1144,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>56</v>
@@ -1148,7 +1152,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24">
         <v>55</v>
@@ -1156,7 +1160,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25">
         <v>55</v>
@@ -1164,7 +1168,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26">
         <v>53</v>
@@ -1172,7 +1176,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27">
         <v>53</v>
@@ -1180,7 +1184,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28">
         <v>52</v>
@@ -1188,7 +1192,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29">
         <v>52</v>
@@ -1196,7 +1200,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>52</v>
@@ -1204,7 +1208,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>51</v>
@@ -1212,7 +1216,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32">
         <v>50</v>
@@ -1220,7 +1224,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33">
         <v>50</v>
@@ -1228,7 +1232,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34">
         <v>49</v>
@@ -1236,7 +1240,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35">
         <v>47</v>
@@ -1244,7 +1248,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36">
         <v>46</v>
@@ -1252,7 +1256,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37">
         <v>45</v>
@@ -1260,7 +1264,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38">
         <v>45</v>
@@ -1268,7 +1272,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39">
         <v>44</v>
@@ -1276,7 +1280,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40">
         <v>44</v>
@@ -1284,7 +1288,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41">
         <v>44</v>
@@ -1292,7 +1296,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42">
         <v>43</v>
@@ -1300,7 +1304,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43">
         <v>43</v>
@@ -1308,7 +1312,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44">
         <v>42</v>
@@ -1316,7 +1320,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45">
         <v>42</v>
@@ -1324,7 +1328,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46">
         <v>42</v>
@@ -1332,7 +1336,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47">
         <v>41</v>
@@ -1340,7 +1344,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48">
         <v>41</v>
@@ -1348,7 +1352,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49">
         <v>40</v>
@@ -1356,7 +1360,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50">
         <v>40</v>
@@ -1364,7 +1368,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51">
         <v>39</v>
@@ -1372,7 +1376,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52">
         <v>39</v>
@@ -1380,7 +1384,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B53">
         <v>39</v>
@@ -1388,7 +1392,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B54">
         <v>38</v>
@@ -1396,7 +1400,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55">
         <v>38</v>
@@ -1404,7 +1408,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56">
         <v>37</v>
@@ -1412,7 +1416,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57">
         <v>36</v>
@@ -1420,7 +1424,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B58">
         <v>36</v>
@@ -1428,7 +1432,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59">
         <v>34</v>
@@ -1436,7 +1440,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60">
         <v>33</v>
@@ -1444,7 +1448,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B61">
         <v>33</v>
@@ -1452,7 +1456,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62">
         <v>33</v>
@@ -1460,7 +1464,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B63">
         <v>32</v>
@@ -1468,7 +1472,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B64">
         <v>32</v>
@@ -1476,7 +1480,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B65">
         <v>31</v>
@@ -1484,7 +1488,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66">
         <v>31</v>
@@ -1492,7 +1496,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B67">
         <v>30</v>
@@ -1500,7 +1504,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68">
         <v>30</v>
@@ -1508,7 +1512,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69">
         <v>30</v>
@@ -1516,7 +1520,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B70">
         <v>30</v>
@@ -1524,7 +1528,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B71">
         <v>30</v>
@@ -1532,7 +1536,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B72">
         <v>29</v>
@@ -1540,7 +1544,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B73">
         <v>29</v>
@@ -1548,7 +1552,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B74">
         <v>28</v>
@@ -1556,7 +1560,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B75">
         <v>28</v>
@@ -1564,7 +1568,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B76">
         <v>28</v>
@@ -1572,7 +1576,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B77">
         <v>28</v>
@@ -1580,7 +1584,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B78">
         <v>27</v>
@@ -1588,7 +1592,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B79">
         <v>26</v>
@@ -1596,7 +1600,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B80">
         <v>26</v>
@@ -1604,7 +1608,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B81">
         <v>25</v>
@@ -1612,7 +1616,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B82">
         <v>26</v>
@@ -1620,7 +1624,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B83">
         <v>26</v>
@@ -1628,7 +1632,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84">
         <v>26</v>
@@ -1636,7 +1640,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B85">
         <v>26</v>
@@ -1644,7 +1648,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B86">
         <v>25</v>
@@ -1652,7 +1656,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B87">
         <v>26</v>
@@ -1660,7 +1664,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B88">
         <v>26</v>
@@ -1668,7 +1672,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B89">
         <v>25</v>
@@ -1676,7 +1680,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B90">
         <v>25</v>
@@ -1684,7 +1688,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B91">
         <v>25</v>
@@ -1692,7 +1696,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B92">
         <v>25</v>
@@ -1700,7 +1704,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B93">
         <v>25</v>
@@ -1708,7 +1712,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B94">
         <v>24</v>
@@ -1716,7 +1720,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B95">
         <v>24</v>
@@ -1724,7 +1728,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B96">
         <v>23</v>
@@ -1732,7 +1736,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B97">
         <v>22</v>
@@ -1740,7 +1744,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B98">
         <v>22</v>
@@ -1748,7 +1752,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B99">
         <v>22</v>
@@ -1756,7 +1760,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B100">
         <v>20</v>
@@ -1764,7 +1768,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B101">
         <v>22</v>
@@ -1772,7 +1776,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B102">
         <v>20</v>
@@ -1780,7 +1784,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B103">
         <v>20</v>
@@ -1788,7 +1792,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B104">
         <v>19</v>
@@ -1796,7 +1800,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B105">
         <v>19</v>
@@ -1804,7 +1808,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B106">
         <v>19</v>
@@ -1812,7 +1816,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B107">
         <v>18</v>
@@ -1820,7 +1824,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B108">
         <v>17</v>
@@ -1828,7 +1832,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B109">
         <v>17</v>
@@ -1836,7 +1840,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B110">
         <v>17</v>
@@ -1844,7 +1848,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B111">
         <v>17</v>
@@ -1852,7 +1856,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B112">
         <v>17</v>
@@ -1860,7 +1864,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113">
         <v>16</v>
@@ -1868,7 +1872,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B114">
         <v>16</v>
@@ -1876,7 +1880,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B115">
         <v>16</v>
@@ -1884,7 +1888,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B116">
         <v>15</v>
@@ -1892,7 +1896,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B117">
         <v>15</v>
@@ -1900,7 +1904,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B118">
         <v>15</v>
@@ -1908,7 +1912,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B119">
         <v>15</v>
@@ -1916,7 +1920,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B120">
         <v>14</v>
@@ -1924,7 +1928,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B121">
         <v>14</v>
@@ -1932,7 +1936,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B122">
         <v>14</v>
@@ -1940,7 +1944,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B123">
         <v>14</v>
@@ -1948,7 +1952,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B124">
         <v>13</v>
@@ -1956,7 +1960,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B125">
         <v>13</v>
@@ -1964,7 +1968,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B126">
         <v>13</v>
@@ -1972,7 +1976,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B127">
         <v>13</v>
@@ -1980,7 +1984,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B128">
         <v>13</v>
@@ -1988,7 +1992,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B129">
         <v>13</v>
@@ -1996,7 +2000,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B130">
         <v>13</v>
@@ -2004,7 +2008,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B131">
         <v>13</v>
@@ -2012,7 +2016,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B132">
         <v>12</v>
@@ -2020,7 +2024,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B133">
         <v>12</v>
@@ -2028,7 +2032,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B134">
         <v>12</v>
@@ -2036,7 +2040,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B135">
         <v>12</v>
@@ -2044,7 +2048,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B136">
         <v>12</v>
@@ -2052,7 +2056,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B137">
         <v>12</v>
@@ -2060,7 +2064,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B138">
         <v>12</v>
@@ -2068,7 +2072,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B139">
         <v>12</v>
@@ -2076,7 +2080,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B140">
         <v>12</v>
@@ -2084,7 +2088,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141">
         <v>12</v>
@@ -2092,7 +2096,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B142">
         <v>11</v>
@@ -2100,7 +2104,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B143">
         <v>11</v>
@@ -2108,7 +2112,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B144">
         <v>11</v>
@@ -2116,7 +2120,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B145">
         <v>11</v>
@@ -2124,7 +2128,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B146">
         <v>10</v>
@@ -2132,7 +2136,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B147">
         <v>10</v>
@@ -2140,7 +2144,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B148">
         <v>10</v>
@@ -2148,7 +2152,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B149">
         <v>10</v>
@@ -2156,7 +2160,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B150">
         <v>10</v>
@@ -2164,7 +2168,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B151">
         <v>10</v>
@@ -2172,7 +2176,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B152">
         <v>10</v>
@@ -2180,7 +2184,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B153">
         <v>10</v>
@@ -2188,7 +2192,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B154">
         <v>10</v>
@@ -2196,7 +2200,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B155">
         <v>10</v>
@@ -2204,7 +2208,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B156">
         <v>10</v>
@@ -2212,7 +2216,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B157">
         <v>9</v>
@@ -2220,7 +2224,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B158">
         <v>9</v>
@@ -2228,7 +2232,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B159">
         <v>8</v>
@@ -2236,7 +2240,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B160">
         <v>8</v>
@@ -2244,7 +2248,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B161">
         <v>7</v>
@@ -2252,7 +2256,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B162">
         <v>7</v>
@@ -2260,7 +2264,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B163">
         <v>7</v>
@@ -2268,7 +2272,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B164">
         <v>7</v>
@@ -2276,7 +2280,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B165">
         <v>7</v>
@@ -2284,7 +2288,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B166">
         <v>7</v>
@@ -2292,7 +2296,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B167">
         <v>7</v>
@@ -2300,7 +2304,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B168">
         <v>6</v>
@@ -2308,7 +2312,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B169">
         <v>6</v>
@@ -2316,7 +2320,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B170">
         <v>6</v>
@@ -2324,7 +2328,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B171">
         <v>5</v>
@@ -2332,7 +2336,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B172">
         <v>5</v>
@@ -2340,7 +2344,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B173">
         <v>5</v>
@@ -2348,7 +2352,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B174">
         <v>5</v>
@@ -2356,7 +2360,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B175">
         <v>5</v>
@@ -2364,7 +2368,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B176">
         <v>5</v>
@@ -2372,7 +2376,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B177">
         <v>4</v>
@@ -2380,7 +2384,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B178">
         <v>4</v>
@@ -2388,7 +2392,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B179">
         <v>4</v>
@@ -2396,7 +2400,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B180">
         <v>4</v>
@@ -2404,7 +2408,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B181">
         <v>3</v>
@@ -2412,7 +2416,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B182">
         <v>3</v>
@@ -2420,7 +2424,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B183">
         <v>3</v>
@@ -2428,7 +2432,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B184">
         <v>3</v>
@@ -2436,7 +2440,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B185">
         <v>6</v>
